--- a/JOIN  NOTES.xlsx
+++ b/JOIN  NOTES.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Desktop\Tops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFECE780-D59C-46EF-AE99-F420D732044B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E4B120-B4F6-459F-99D4-7C2F19D8A426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8F21CF83-5F06-4E62-A544-7CB542314EA8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{8F21CF83-5F06-4E62-A544-7CB542314EA8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="21">
   <si>
     <t>EMPLOYEES</t>
   </si>
@@ -91,6 +92,12 @@
   </si>
   <si>
     <t>NAME</t>
+  </si>
+  <si>
+    <t>TABLE1</t>
+  </si>
+  <si>
+    <t>TABLE2</t>
   </si>
 </sst>
 </file>
@@ -722,4 +729,51 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F9A3694-B165-4957-AC57-15E29BD3B689}">
+  <dimension ref="A3:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C7">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>